--- a/artfynd/A 11578-2025 artfynd.xlsx
+++ b/artfynd/A 11578-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,113 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123230729</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>585444</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7041040</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11578-2025 artfynd.xlsx
+++ b/artfynd/A 11578-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123230729</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 11578-2025 artfynd.xlsx
+++ b/artfynd/A 11578-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123230729</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 11578-2025 artfynd.xlsx
+++ b/artfynd/A 11578-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123230729</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 11578-2025 artfynd.xlsx
+++ b/artfynd/A 11578-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>123230729</v>
       </c>
       <c r="B3" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 11578-2025 artfynd.xlsx
+++ b/artfynd/A 11578-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119272377</v>
+        <v>119272324</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585391</v>
+        <v>585370</v>
       </c>
       <c r="R2" t="n">
-        <v>7041074</v>
+        <v>7041067</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123230729</v>
+        <v>119274139</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långstranden, Långstranden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585444</v>
+        <v>585462</v>
       </c>
       <c r="R3" t="n">
-        <v>7041040</v>
+        <v>7040940</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -867,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,15 +857,724 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>119272515</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>585367</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7041044</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123230729</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>585444</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7041040</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Daniel Rutschman</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Daniel Rutschman</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123230826</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>585407</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7041101</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119272377</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>585391</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7041074</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119273514</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>585442</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7040958</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>119273322</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>585405</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7040985</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>119273474</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långstranden, Långstranden, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>585436</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7040951</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11578-2025 artfynd.xlsx
+++ b/artfynd/A 11578-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119272324</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119274139</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119272515</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123230729</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123230826</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119272377</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119273514</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119273322</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,8 +1620,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119273474</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>